--- a/public/assets/templates/operasional/capacitor_bank.xlsx
+++ b/public/assets/templates/operasional/capacitor_bank.xlsx
@@ -1,40 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajad\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46602E6C-6BBC-44EA-898A-04CF5C152433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{19C9C3F9-33B8-4BF8-98FC-8FDB0880133D}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
+    <sheet name="Lembar1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
   <si>
     <t>PT BUMI ALAM SEGAR</t>
   </si>
@@ -71,31 +52,40 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Arial"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <u val="none"/>
       </rPr>
-      <t>Suhu Ruang
+      <t xml:space="preserve">Suhu Ruang
 (</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Times New Roman"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <u val="none"/>
       </rPr>
-      <t>℃</t>
+      <t xml:space="preserve">℃</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Arial"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <u val="none"/>
       </rPr>
-      <t>)</t>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -120,45 +110,64 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="SimSun"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -179,44 +188,44 @@
     </border>
     <border>
       <left style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -224,7 +233,7 @@
       <left/>
       <right/>
       <top style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -232,54 +241,54 @@
     <border>
       <left/>
       <right style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -288,18 +297,18 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -307,7 +316,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -315,97 +324,97 @@
     <border>
       <left/>
       <right style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="double">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -413,115 +422,110 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+  <cellXfs count="33">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="7" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="14" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="7" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="14" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="16" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="18" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -530,25 +534,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>265430</xdr:colOff>
+      <xdr:colOff>266700</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>42545</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>348615</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="Logo PT.BAS">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5279EBE-4B18-445E-BF2D-3B0D7203FF7C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1" name="Picture 2" descr="Logo PT.BAS"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -560,9 +558,8 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7631430" y="42545"/>
-          <a:ext cx="1302385" cy="351155"/>
+        <a:xfrm rot="0">
+          <a:ext cx="1304925" cy="352425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -575,7 +572,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -617,7 +614,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -669,7 +666,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -730,151 +727,178 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{638A6E9A-A0BA-428D-8D75-70723327A202}">
-  <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:R46"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" customHeight="1" ht="15">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -898,7 +922,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -918,7 +942,7 @@
       <c r="Q2" s="11"/>
       <c r="R2" s="12"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -942,7 +966,7 @@
       <c r="Q3" s="13"/>
       <c r="R3" s="14"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -962,7 +986,7 @@
       <c r="Q4" s="11"/>
       <c r="R4" s="12"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18">
       <c r="A5" s="15" t="s">
         <v>4</v>
       </c>
@@ -1006,7 +1030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" customHeight="1" ht="30">
       <c r="A6" s="15"/>
       <c r="B6" s="9"/>
       <c r="C6" s="16"/>
@@ -1044,7 +1068,7 @@
       <c r="Q6" s="18"/>
       <c r="R6" s="19"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18">
       <c r="A7" s="22">
         <v>1</v>
       </c>
@@ -1066,7 +1090,7 @@
       <c r="Q7" s="24"/>
       <c r="R7" s="25"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18">
       <c r="A8" s="22">
         <v>2</v>
       </c>
@@ -1088,7 +1112,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="25"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18">
       <c r="A9" s="22">
         <v>3</v>
       </c>
@@ -1110,7 +1134,7 @@
       <c r="Q9" s="24"/>
       <c r="R9" s="25"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18">
       <c r="A10" s="22">
         <v>4</v>
       </c>
@@ -1132,7 +1156,7 @@
       <c r="Q10" s="24"/>
       <c r="R10" s="25"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18">
       <c r="A11" s="22">
         <v>5</v>
       </c>
@@ -1154,7 +1178,7 @@
       <c r="Q11" s="24"/>
       <c r="R11" s="25"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18">
       <c r="A12" s="22">
         <v>6</v>
       </c>
@@ -1176,7 +1200,7 @@
       <c r="Q12" s="24"/>
       <c r="R12" s="25"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18">
       <c r="A13" s="22">
         <v>7</v>
       </c>
@@ -1198,7 +1222,7 @@
       <c r="Q13" s="24"/>
       <c r="R13" s="25"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18">
       <c r="A14" s="22">
         <v>8</v>
       </c>
@@ -1220,7 +1244,7 @@
       <c r="Q14" s="24"/>
       <c r="R14" s="25"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18">
       <c r="A15" s="22">
         <v>9</v>
       </c>
@@ -1242,7 +1266,7 @@
       <c r="Q15" s="24"/>
       <c r="R15" s="25"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18">
       <c r="A16" s="22">
         <v>10</v>
       </c>
@@ -1264,7 +1288,7 @@
       <c r="Q16" s="24"/>
       <c r="R16" s="25"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18">
       <c r="A17" s="22">
         <v>11</v>
       </c>
@@ -1286,7 +1310,7 @@
       <c r="Q17" s="24"/>
       <c r="R17" s="25"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18">
       <c r="A18" s="22">
         <v>12</v>
       </c>
@@ -1308,7 +1332,7 @@
       <c r="Q18" s="26"/>
       <c r="R18" s="25"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18">
       <c r="A19" s="22">
         <v>13</v>
       </c>
@@ -1330,7 +1354,7 @@
       <c r="Q19" s="24"/>
       <c r="R19" s="25"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18">
       <c r="A20" s="22">
         <v>14</v>
       </c>
@@ -1352,7 +1376,7 @@
       <c r="Q20" s="24"/>
       <c r="R20" s="25"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18">
       <c r="A21" s="22">
         <v>15</v>
       </c>
@@ -1374,7 +1398,7 @@
       <c r="Q21" s="24"/>
       <c r="R21" s="25"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18">
       <c r="A22" s="22">
         <v>16</v>
       </c>
@@ -1396,7 +1420,7 @@
       <c r="Q22" s="24"/>
       <c r="R22" s="25"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18">
       <c r="A23" s="22">
         <v>17</v>
       </c>
@@ -1418,7 +1442,7 @@
       <c r="Q23" s="24"/>
       <c r="R23" s="25"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18">
       <c r="A24" s="22">
         <v>18</v>
       </c>
@@ -1440,7 +1464,7 @@
       <c r="Q24" s="24"/>
       <c r="R24" s="25"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18">
       <c r="A25" s="22">
         <v>19</v>
       </c>
@@ -1462,7 +1486,7 @@
       <c r="Q25" s="24"/>
       <c r="R25" s="25"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18">
       <c r="A26" s="22">
         <v>20</v>
       </c>
@@ -1484,7 +1508,7 @@
       <c r="Q26" s="24"/>
       <c r="R26" s="25"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18">
       <c r="A27" s="22">
         <v>21</v>
       </c>
@@ -1506,7 +1530,7 @@
       <c r="Q27" s="24"/>
       <c r="R27" s="25"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18">
       <c r="A28" s="22">
         <v>22</v>
       </c>
@@ -1528,7 +1552,7 @@
       <c r="Q28" s="24"/>
       <c r="R28" s="25"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18">
       <c r="A29" s="22">
         <v>23</v>
       </c>
@@ -1550,7 +1574,7 @@
       <c r="Q29" s="24"/>
       <c r="R29" s="25"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18">
       <c r="A30" s="22">
         <v>24</v>
       </c>
@@ -1572,7 +1596,7 @@
       <c r="Q30" s="24"/>
       <c r="R30" s="25"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18">
       <c r="A31" s="22">
         <v>25</v>
       </c>
@@ -1594,7 +1618,7 @@
       <c r="Q31" s="24"/>
       <c r="R31" s="25"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18">
       <c r="A32" s="22">
         <v>26</v>
       </c>
@@ -1616,7 +1640,7 @@
       <c r="Q32" s="24"/>
       <c r="R32" s="25"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18">
       <c r="A33" s="22">
         <v>27</v>
       </c>
@@ -1638,7 +1662,7 @@
       <c r="Q33" s="24"/>
       <c r="R33" s="25"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18">
       <c r="A34" s="22">
         <v>28</v>
       </c>
@@ -1660,7 +1684,7 @@
       <c r="Q34" s="24"/>
       <c r="R34" s="25"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18">
       <c r="A35" s="22">
         <v>29</v>
       </c>
@@ -1682,7 +1706,7 @@
       <c r="Q35" s="24"/>
       <c r="R35" s="25"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18">
       <c r="A36" s="22">
         <v>30</v>
       </c>
@@ -1704,7 +1728,7 @@
       <c r="Q36" s="24"/>
       <c r="R36" s="25"/>
     </row>
-    <row r="37" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:18" customHeight="1" ht="15">
       <c r="A37" s="27">
         <v>31</v>
       </c>
@@ -1726,7 +1750,7 @@
       <c r="Q37" s="28"/>
       <c r="R37" s="29"/>
     </row>
-    <row r="38" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" customHeight="1" ht="15">
       <c r="A38" s="30"/>
       <c r="B38" s="30"/>
       <c r="C38" s="30"/>
@@ -1741,16 +1765,21 @@
       <c r="L38" s="30"/>
       <c r="M38" s="30"/>
       <c r="N38" s="30"/>
-      <c r="O38" s="31" t="s">
-        <v>17</v>
-      </c>
+      <c r="O38" s="31"/>
       <c r="P38" s="31"/>
       <c r="Q38" s="31"/>
       <c r="R38" s="31"/>
     </row>
+    <row r="46" spans="1:18">
+      <c r="O46" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="O38:R38"/>
+  <mergeCells>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:O5"/>
@@ -1770,8 +1799,11 @@
     <mergeCell ref="D3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:R4"/>
+    <mergeCell ref="O46:R46"/>
   </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>